--- a/1-LATEX/2-DADOS/3-OUTPUT/trimfill.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/trimfill.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,16 +418,16 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>0.04486941313379269</v>
+        <v>0.06290875280931077</v>
       </c>
       <c r="E3">
-        <v>0.04486941313379269</v>
+        <v>0.07380347689889237</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1.095428770928103</v>
       </c>
     </row>
     <row r="4">
@@ -443,13 +443,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>0.0715760285814679</v>
+        <v>0.007406380896008698</v>
       </c>
       <c r="E4">
-        <v>0.2295737715397972</v>
+        <v>0.2516522954497213</v>
       </c>
       <c r="F4">
-        <v>17.11635513397477</v>
+        <v>27.66582407318374</v>
       </c>
     </row>
     <row r="5">
@@ -462,38 +462,60 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>0.007406380896008698</v>
+        <v>-0.2787298060244909</v>
       </c>
       <c r="E5">
-        <v>0.2516522954497213</v>
+        <v>-0.5007540510359201</v>
       </c>
       <c r="F5">
-        <v>27.66582407318374</v>
+        <v>-19.91040536321075</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="B6">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>-0.2787298060244909</v>
+        <v>0.05120757701632275</v>
       </c>
       <c r="E6">
-        <v>-0.5007540510359201</v>
+        <v>0.07474737412956359</v>
       </c>
       <c r="F6">
-        <v>-19.91040536321075</v>
+        <v>2.38190449783436</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>47</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>0.2796759134695573</v>
+      </c>
+      <c r="E7">
+        <v>0.3420252682759156</v>
+      </c>
+      <c r="F7">
+        <v>6.433411002216357</v>
       </c>
     </row>
   </sheetData>
